--- a/data/trans_camb/P16A04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,6</t>
+          <t>2,66; 9,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,32</t>
+          <t>-0,02; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,56</t>
+          <t>-1,43; 0,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,46</t>
+          <t>0,85; 8,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,47</t>
+          <t>-2,49; 3,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,47</t>
+          <t>-3,05; 2,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,62</t>
+          <t>2,54; 7,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,44</t>
+          <t>-0,89; 2,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,23</t>
+          <t>-1,57; 1,19</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 668,94</t>
+          <t>3,09; 528,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 262,43</t>
+          <t>-61,32; 233,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,08; 181,43</t>
+          <t>-72,23; 255,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>103,13; 1026,44</t>
+          <t>89,11; 878,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 349,83</t>
+          <t>-42,28; 319,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 182,97</t>
+          <t>-71,19; 165,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,64</t>
+          <t>-0,91; 2,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,38</t>
+          <t>-0,81; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,14</t>
+          <t>-1,1; 2,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,04</t>
+          <t>-3,68; -0,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,13</t>
+          <t>-3,67; -0,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,82</t>
+          <t>-2,83; 0,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,71</t>
+          <t>-1,65; 0,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,77</t>
+          <t>-1,61; 0,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,91</t>
+          <t>-1,36; 0,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 548,23</t>
+          <t>-63,78; 583,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 437,84</t>
+          <t>-50,32; 428,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,06; 391,46</t>
+          <t>-68,65; 415,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 5,68</t>
+          <t>-85,02; 15,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,81; 5,25</t>
+          <t>-83,97; 11,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,58; 47,35</t>
+          <t>-64,39; 34,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,45; 48,18</t>
+          <t>-61,5; 57,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,75; 53,36</t>
+          <t>-58,81; 49,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 60,89</t>
+          <t>-52,83; 59,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,75</t>
+          <t>-0,01; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,2</t>
+          <t>0,61; 4,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,44</t>
+          <t>2,49; 7,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,54</t>
+          <t>-0,28; 3,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,09</t>
+          <t>-0,54; 2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,31</t>
+          <t>2,19; 6,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,46</t>
+          <t>0,28; 2,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,93</t>
+          <t>0,42; 2,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,25</t>
+          <t>2,85; 5,94</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,7; inf</t>
+          <t>-49,43; 1278,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,32; inf</t>
+          <t>-56,86; 900,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,93; 1807,83</t>
+          <t>102,09; 2049,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 1230,87</t>
+          <t>0,47; 1241,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,95; 1551,58</t>
+          <t>14,02; 1301,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>220,3; 3498,23</t>
+          <t>212,64; 3042,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,35</t>
+          <t>-0,88; 4,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,89</t>
+          <t>-1,38; 2,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,11</t>
+          <t>-2,68; 1,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,29</t>
+          <t>-2,68; 2,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,07</t>
+          <t>-3,1; 2,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,29</t>
+          <t>-4,49; -0,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,51</t>
+          <t>-1,31; 2,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,65</t>
+          <t>-1,72; 1,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; -0,13</t>
+          <t>-2,97; -0,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 434,07</t>
+          <t>-42,03; 452,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,47; 372,98</t>
+          <t>-55,53; 374,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-97,74; 319,33</t>
+          <t>-97,98; 269,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 124,62</t>
+          <t>-61,06; 121,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 125,75</t>
+          <t>-68,24; 124,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,24; -7,07</t>
+          <t>-89,73; -2,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,37; 140,56</t>
+          <t>-41,23; 125,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 97,65</t>
+          <t>-51,2; 84,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 0,01</t>
+          <t>-82,81; 6,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,21</t>
+          <t>1,59; 9,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,23</t>
+          <t>-0,44; 3,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,54</t>
+          <t>-1,02; 1,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 6,81</t>
+          <t>-1,02; 6,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,81</t>
+          <t>-2,39; 3,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,03</t>
+          <t>-3,4; 1,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,77</t>
+          <t>1,03; 6,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,81</t>
+          <t>-0,96; 2,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,43</t>
+          <t>-1,48; 1,49</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 633,78</t>
+          <t>-40,46; 660,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,19; 417,65</t>
+          <t>-66,27; 458,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 274,73</t>
+          <t>-71,79; 194,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,59; 856,75</t>
+          <t>23,62; 960,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 364,32</t>
+          <t>-52,51; 416,32</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,75; 220,76</t>
+          <t>-58,53; 251,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,77</t>
+          <t>-2,06; 1,82</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,75</t>
+          <t>-1,96; 1,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,99</t>
+          <t>0,43; 5,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,38</t>
+          <t>-3,66; 1,38</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,63</t>
+          <t>-4,34; 0,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,98</t>
+          <t>-0,82; 5,12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,99</t>
+          <t>-2,18; 1,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,63</t>
+          <t>-2,43; 0,63</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,44</t>
+          <t>0,55; 4,51</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 492,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 1165,76</t>
+          <t>2,2; 1263,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,32</t>
+          <t>-100,0; 66,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 464,18</t>
+          <t>-24,57; 519,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,51; 100,5</t>
+          <t>-80,49; 102,83</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,13; 70,22</t>
+          <t>-82,34; 70,7</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19,85; 396,27</t>
+          <t>3,68; 356,57</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,16</t>
+          <t>-1,78; 1,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,32</t>
+          <t>-0,37; 3,48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,09</t>
+          <t>0,88; 5,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,38</t>
+          <t>-0,21; 2,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,47</t>
+          <t>0,48; 3,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,26</t>
+          <t>1,17; 6,48</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,27</t>
+          <t>-0,54; 1,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,96</t>
+          <t>0,54; 2,88</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,07</t>
+          <t>1,63; 5,05</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 113,23</t>
+          <t>-70,13; 120,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 293,84</t>
+          <t>-20,8; 307,74</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21,39; 440,8</t>
+          <t>26,42; 450,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 558,97</t>
+          <t>-26,21; 549,28</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,17; 754,82</t>
+          <t>-0,76; 806,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>87,92; 1183,82</t>
+          <t>101,46; 1286,8</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 131,49</t>
+          <t>-32,52; 177,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,27; 325,18</t>
+          <t>20,8; 324,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>91,62; 545,2</t>
+          <t>99,04; 553,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,36</t>
+          <t>-2,06; 2,18</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; -0,97</t>
+          <t>-4,36; -0,94</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,76</t>
+          <t>-4,96; -1,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,57</t>
+          <t>-0,8; 2,61</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,25</t>
+          <t>-1,88; 1,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,01</t>
+          <t>-2,25; 2,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,85</t>
+          <t>-0,9; 1,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -0,27</t>
+          <t>-2,47; -0,22</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,68</t>
+          <t>-3,24; -0,74</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 82,71</t>
+          <t>-40,66; 80,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -26,69</t>
+          <t>-85,7; -29,37</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,38; -51,54</t>
+          <t>-96,14; -45,1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 159,82</t>
+          <t>-27,3; 154,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-56,43; 76,95</t>
+          <t>-57,41; 89,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 131,82</t>
+          <t>-75,9; 128,28</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 73,78</t>
+          <t>-23,92; 69,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-66,64; -9,17</t>
+          <t>-63,15; -6,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,65; -18,28</t>
+          <t>-84,81; -17,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,9</t>
+          <t>0,3; 1,87</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,92</t>
+          <t>-0,42; 0,91</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,1</t>
+          <t>-0,35; 1,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,35</t>
+          <t>-0,07; 1,48</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,76</t>
+          <t>-0,67; 0,78</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,65</t>
+          <t>0,05; 1,69</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,41</t>
+          <t>0,29; 1,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,63</t>
+          <t>-0,38; 0,62</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,16</t>
+          <t>0,06; 1,2</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>11,46; 130,47</t>
+          <t>12,31; 125,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 60,72</t>
+          <t>-18,72; 61,01</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 74,33</t>
+          <t>-17,24; 73,09</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 71,1</t>
+          <t>-4,52; 74,72</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 39,9</t>
+          <t>-26,01; 41,09</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,17; 86,98</t>
+          <t>0,54; 87,84</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,9; 80,93</t>
+          <t>12,99; 78,01</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 36,03</t>
+          <t>-16,79; 34,41</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3,02; 65,44</t>
+          <t>2,75; 67,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A04-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,03</t>
+          <t>2,69; 9,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,36</t>
+          <t>-0,04; 3,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,58</t>
+          <t>-1,37; 0,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,4</t>
+          <t>1,14; 8,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,22</t>
+          <t>-2,58; 3,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,66</t>
+          <t>-2,63; 2,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,83</t>
+          <t>2,67; 7,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,58</t>
+          <t>-0,86; 2,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,19</t>
+          <t>-1,4; 1,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-20,72%</t>
+          <t>-30,3%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,29%</t>
+          <t>-1,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,84%</t>
+          <t>-3,8%</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 528,68</t>
+          <t>16,16; 588,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,32; 233,58</t>
+          <t>-62,39; 224,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 255,98</t>
+          <t>-63,17; 220,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,11; 878,71</t>
+          <t>88,24; 917,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 319,12</t>
+          <t>-42,18; 329,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 165,11</t>
+          <t>-65,62; 181,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,87</t>
+          <t>-0,98; 2,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,39</t>
+          <t>-0,91; 2,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,18</t>
+          <t>-1,17; 2,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,01</t>
+          <t>-3,43; 0,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,02</t>
+          <t>-3,48; 0,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 0,66</t>
+          <t>-2,95; 0,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,83</t>
+          <t>-1,77; 0,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,73</t>
+          <t>-1,67; 0,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,84</t>
+          <t>-1,55; 0,88</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-29,48%</t>
+          <t>-32,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,39%</t>
+          <t>-16,41%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,78; 583,71</t>
+          <t>-66,23; 391,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,32; 428,23</t>
+          <t>-59,78; 416,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 415,15</t>
+          <t>-67,41; 451,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 15,83</t>
+          <t>-83,08; 15,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,97; 11,82</t>
+          <t>-83,19; 9,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,39; 34,33</t>
+          <t>-67,33; 44,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 57,74</t>
+          <t>-63,04; 50,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 49,1</t>
+          <t>-61,83; 38,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,83; 59,42</t>
+          <t>-54,61; 58,77</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>4,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,74</t>
+          <t>-0,02; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,16</t>
+          <t>0,6; 4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,17</t>
+          <t>2,25; 6,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,66</t>
+          <t>-0,29; 3,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,89</t>
+          <t>-0,52; 3,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,15</t>
+          <t>2,29; 6,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,53</t>
+          <t>0,19; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,86</t>
+          <t>0,49; 3,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,94</t>
+          <t>2,74; 5,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1502,55%</t>
+          <t>1408,79%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>464,9%</t>
+          <t>477,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>720,79%</t>
+          <t>708,41%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 1278,88</t>
+          <t>-49,2; inf</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 900,87</t>
+          <t>-62,79; 877,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102,09; 2049,0</t>
+          <t>100,94; 2118,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1241,36</t>
+          <t>-1,4; 1267,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 1301,19</t>
+          <t>17,75; 1403,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212,64; 3042,32</t>
+          <t>207,56; 2954,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,43</t>
+          <t>-0,81; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,96</t>
+          <t>-1,35; 2,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,17</t>
+          <t>-2,26; 1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,49</t>
+          <t>-2,93; 2,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,2</t>
+          <t>-3,53; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,34</t>
+          <t>-3,88; 0,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,28</t>
+          <t>-1,24; 2,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,53</t>
+          <t>-1,64; 1,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; -0,21</t>
+          <t>-2,57; 0,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-51,04%</t>
+          <t>-30,39%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-64,81%</t>
+          <t>-46,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-59,05%</t>
+          <t>-40,59%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 452,63</t>
+          <t>-42,48; 414,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,53; 374,99</t>
+          <t>-56,05; 295,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-97,98; 269,22</t>
+          <t>-92,1; 274,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 121,18</t>
+          <t>-66,25; 128,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 124,29</t>
+          <t>-72,23; 100,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,73; -2,97</t>
+          <t>-82,52; 48,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 125,25</t>
+          <t>-39,58; 146,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 84,84</t>
+          <t>-50,29; 88,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 6,79</t>
+          <t>-74,69; 35,43</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,45</t>
+          <t>1,9; 9,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,99</t>
+          <t>-0,43; 4,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,55</t>
+          <t>-0,97; 1,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 6,63</t>
+          <t>-1,19; 6,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,79</t>
+          <t>-2,74; 3,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,9</t>
+          <t>-3,09; 2,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,45</t>
+          <t>1,16; 6,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,8</t>
+          <t>-0,86; 2,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,49</t>
+          <t>-1,48; 1,19</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-5,74%</t>
+          <t>-9,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,46; 660,82</t>
+          <t>-40,53; 544,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 458,6</t>
+          <t>-75,77; 483,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,79; 194,66</t>
+          <t>-69,09; 263,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,62; 960,42</t>
+          <t>17,42; 839,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 416,32</t>
+          <t>-52,25; 442,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 251,76</t>
+          <t>-62,06; 209,88</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>2,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,82</t>
+          <t>-2,11; 1,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,96</t>
+          <t>-1,91; 1,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,5</t>
+          <t>0,3; 5,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,38</t>
+          <t>-3,74; 1,28</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,23</t>
+          <t>-4,09; 0,54</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 5,12</t>
+          <t>-0,78; 4,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,08</t>
+          <t>-2,22; 0,92</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,63</t>
+          <t>-2,53; 0,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,51</t>
+          <t>0,47; 4,31</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>217,22%</t>
+          <t>209,71%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>131,08%</t>
+          <t>128,59%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,8; 546,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,49; 510,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2,2; 1263,84</t>
+          <t>-10,02; 1110,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 214,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,84</t>
+          <t>-100,0; 104,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 519,82</t>
+          <t>-26,28; 453,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-80,49; 102,83</t>
+          <t>-79,78; 98,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-82,34; 70,7</t>
+          <t>-81,39; 56,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,68; 356,57</t>
+          <t>7,34; 362,89</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>3,04</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>4,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,17</t>
+          <t>-1,79; 1,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,48</t>
+          <t>-0,3; 3,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,43</t>
+          <t>0,81; 5,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,44</t>
+          <t>-0,25; 2,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,6</t>
+          <t>0,45; 3,6</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,48</t>
+          <t>4,29; 7,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,41</t>
+          <t>-0,57; 1,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,88</t>
+          <t>0,56; 2,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,05</t>
+          <t>3,31; 6,05</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>163,55%</t>
+          <t>172,08%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>454,8%</t>
+          <t>674,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>266,71%</t>
+          <t>348,23%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 120,18</t>
+          <t>-70,26; 121,4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 307,74</t>
+          <t>-17,87; 315,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26,42; 450,15</t>
+          <t>19,22; 495,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 549,28</t>
+          <t>-39,78; 466,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 806,04</t>
+          <t>4,77; 724,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>101,46; 1286,8</t>
+          <t>230,14; 1721,8</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 177,51</t>
+          <t>-34,19; 145,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,8; 324,6</t>
+          <t>23,94; 315,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>99,04; 553,42</t>
+          <t>162,25; 656,5</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-2,26</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,18</t>
+          <t>-1,97; 2,17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,94</t>
+          <t>-4,27; -1,07</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -1,58</t>
+          <t>-4,73; -1,62</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,61</t>
+          <t>-0,92; 2,52</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,43</t>
+          <t>-1,69; 1,49</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,0</t>
+          <t>-2,93; -0,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,79</t>
+          <t>-0,82; 1,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -0,22</t>
+          <t>-2,38; -0,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,74</t>
+          <t>-3,3; -1,24</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-83,71%</t>
+          <t>-79,18%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-32,65%</t>
+          <t>-62,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-65,76%</t>
+          <t>-72,34%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-40,66; 80,62</t>
+          <t>-40,5; 69,3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-85,7; -29,37</t>
+          <t>-85,53; -35,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,14; -45,1</t>
+          <t>-94,46; -46,38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 154,48</t>
+          <t>-28,55; 163,8</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 89,76</t>
+          <t>-53,4; 99,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-75,9; 128,28</t>
+          <t>-82,73; -17,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 69,09</t>
+          <t>-22,25; 78,64</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-63,15; -6,63</t>
+          <t>-64,96; -6,93</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,81; -17,37</t>
+          <t>-84,6; -47,39</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,14 +2377,14 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
           <t>0,14</t>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,87</t>
+          <t>0,3; 1,81</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,91</t>
+          <t>-0,4; 0,92</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,11</t>
+          <t>-0,17; 1,29</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,48</t>
+          <t>-0,06; 1,47</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,78</t>
+          <t>-0,74; 0,81</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,69</t>
+          <t>0,41; 1,82</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,36</t>
+          <t>0,31; 1,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,62</t>
+          <t>-0,37; 0,65</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,2</t>
+          <t>0,29; 1,31</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>12,31; 125,44</t>
+          <t>13,66; 117,55</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 61,01</t>
+          <t>-19,8; 61,16</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 73,09</t>
+          <t>-8,61; 86,0</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 74,72</t>
+          <t>-2,11; 81,2</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-26,01; 41,09</t>
+          <t>-28,23; 42,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,54; 87,84</t>
+          <t>12,82; 101,83</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,99; 78,01</t>
+          <t>13,56; 81,36</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 34,41</t>
+          <t>-16,44; 36,41</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2,75; 67,66</t>
+          <t>13,0; 73,98</t>
         </is>
       </c>
     </row>
